--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183252</v>
+        <v>124183312</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754346</v>
+        <v>754399</v>
       </c>
       <c r="R2" t="n">
-        <v>7264913</v>
+        <v>7265117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183311</v>
+        <v>124183252</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754375</v>
+        <v>754346</v>
       </c>
       <c r="R3" t="n">
-        <v>7264928</v>
+        <v>7264913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183312</v>
+        <v>124183311</v>
       </c>
       <c r="B5" t="n">
         <v>82597</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754399</v>
+        <v>754375</v>
       </c>
       <c r="R5" t="n">
-        <v>7265117</v>
+        <v>7264928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183312</v>
+        <v>124183252</v>
       </c>
       <c r="B2" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754399</v>
+        <v>754346</v>
       </c>
       <c r="R2" t="n">
-        <v>7265117</v>
+        <v>7264913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183252</v>
+        <v>124183312</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754346</v>
+        <v>754399</v>
       </c>
       <c r="R3" t="n">
-        <v>7264913</v>
+        <v>7265117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183255</v>
+        <v>124183311</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754356</v>
+        <v>754375</v>
       </c>
       <c r="R4" t="n">
-        <v>7264891</v>
+        <v>7264928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183311</v>
+        <v>124183255</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754375</v>
+        <v>754356</v>
       </c>
       <c r="R5" t="n">
-        <v>7264928</v>
+        <v>7264891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183252</v>
+        <v>124183311</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754346</v>
+        <v>754375</v>
       </c>
       <c r="R2" t="n">
-        <v>7264913</v>
+        <v>7264928</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183312</v>
+        <v>124183255</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754399</v>
+        <v>754356</v>
       </c>
       <c r="R3" t="n">
-        <v>7265117</v>
+        <v>7264891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183311</v>
+        <v>124183252</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754375</v>
+        <v>754346</v>
       </c>
       <c r="R4" t="n">
-        <v>7264928</v>
+        <v>7264913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183255</v>
+        <v>124183312</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754356</v>
+        <v>754399</v>
       </c>
       <c r="R5" t="n">
-        <v>7264891</v>
+        <v>7265117</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183255</v>
+        <v>124183312</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754356</v>
+        <v>754399</v>
       </c>
       <c r="R3" t="n">
-        <v>7264891</v>
+        <v>7265117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183252</v>
+        <v>124183255</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754346</v>
+        <v>754356</v>
       </c>
       <c r="R4" t="n">
-        <v>7264913</v>
+        <v>7264891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183312</v>
+        <v>124183252</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754399</v>
+        <v>754346</v>
       </c>
       <c r="R5" t="n">
-        <v>7265117</v>
+        <v>7264913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183311</v>
+        <v>124183255</v>
       </c>
       <c r="B2" t="n">
-        <v>82597</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754375</v>
+        <v>754356</v>
       </c>
       <c r="R2" t="n">
-        <v>7264928</v>
+        <v>7264891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183312</v>
+        <v>124183252</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754399</v>
+        <v>754346</v>
       </c>
       <c r="R3" t="n">
-        <v>7265117</v>
+        <v>7264913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183255</v>
+        <v>124183311</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754356</v>
+        <v>754375</v>
       </c>
       <c r="R4" t="n">
-        <v>7264891</v>
+        <v>7264928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183252</v>
+        <v>124183312</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754346</v>
+        <v>754399</v>
       </c>
       <c r="R5" t="n">
-        <v>7264913</v>
+        <v>7265117</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183255</v>
+        <v>124183252</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754356</v>
+        <v>754346</v>
       </c>
       <c r="R2" t="n">
-        <v>7264891</v>
+        <v>7264913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183252</v>
+        <v>124183311</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754346</v>
+        <v>754375</v>
       </c>
       <c r="R3" t="n">
-        <v>7264913</v>
+        <v>7264928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183311</v>
+        <v>124183312</v>
       </c>
       <c r="B4" t="n">
         <v>82597</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754375</v>
+        <v>754399</v>
       </c>
       <c r="R4" t="n">
-        <v>7264928</v>
+        <v>7265117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183312</v>
+        <v>124183255</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754399</v>
+        <v>754356</v>
       </c>
       <c r="R5" t="n">
-        <v>7265117</v>
+        <v>7264891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183252</v>
+        <v>124183312</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754346</v>
+        <v>754399</v>
       </c>
       <c r="R2" t="n">
-        <v>7264913</v>
+        <v>7265117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124183311</v>
+        <v>124183255</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754375</v>
+        <v>754356</v>
       </c>
       <c r="R3" t="n">
-        <v>7264928</v>
+        <v>7264891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183312</v>
+        <v>124183252</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754399</v>
+        <v>754346</v>
       </c>
       <c r="R4" t="n">
-        <v>7265117</v>
+        <v>7264913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183255</v>
+        <v>124183311</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754356</v>
+        <v>754375</v>
       </c>
       <c r="R5" t="n">
-        <v>7264891</v>
+        <v>7264928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183312</v>
+        <v>124183311</v>
       </c>
       <c r="B2" t="n">
         <v>82597</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754399</v>
+        <v>754375</v>
       </c>
       <c r="R2" t="n">
-        <v>7265117</v>
+        <v>7264928</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183252</v>
+        <v>124183312</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754346</v>
+        <v>754399</v>
       </c>
       <c r="R4" t="n">
-        <v>7264913</v>
+        <v>7265117</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183311</v>
+        <v>124183252</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754375</v>
+        <v>754346</v>
       </c>
       <c r="R5" t="n">
-        <v>7264928</v>
+        <v>7264913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 44523-2024 artfynd.xlsx
+++ b/artfynd/A 44523-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124183311</v>
+        <v>124183312</v>
       </c>
       <c r="B2" t="n">
         <v>82597</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754375</v>
+        <v>754399</v>
       </c>
       <c r="R2" t="n">
-        <v>7264928</v>
+        <v>7265117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124183312</v>
+        <v>124183252</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754399</v>
+        <v>754346</v>
       </c>
       <c r="R4" t="n">
-        <v>7265117</v>
+        <v>7264913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124183252</v>
+        <v>124183311</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754346</v>
+        <v>754375</v>
       </c>
       <c r="R5" t="n">
-        <v>7264913</v>
+        <v>7264928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
